--- a/data/output/evaluasi_62.xlsx
+++ b/data/output/evaluasi_62.xlsx
@@ -8,19 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="6200" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="6271" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="6201" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="6202" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="6204" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6209" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6211" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="6212" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6213" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="6207" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="6210" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="6203" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="6205" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="6208" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6205" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6211" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6212" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6213" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6203" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6201" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6208" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6204" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6206" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6207" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6210" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6271" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="6202" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6209" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,20 +485,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.251818922608511</v>
+        <v>-5.450780257483845</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pmtb_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -512,20 +513,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.139324616178921</v>
+        <v>-7.662449773776705</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -540,20 +541,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-5.621615760095073</v>
+        <v>5.353526198555296</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -568,20 +569,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2632044963078328</v>
+        <v>7.11157473944971</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -596,20 +597,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.280745549609608</v>
+        <v>6.351881440283731</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+          <t>adhk_pkp_q3-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -624,20 +625,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2632044963078328</v>
+        <v>5.139324616162506</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -652,20 +653,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.719828535839405</v>
+        <v>-14.07240819670783</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -680,20 +681,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.280745549609608</v>
+        <v>-5.860965559370722</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -708,20 +709,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.500286398503586</v>
+        <v>3.55617207281883</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -736,20 +737,692 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1223925358139846</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>4.289411421976023</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D12" t="n">
+        <v>-34.76662893000474</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.390276117611988</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>62</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-15.46763291535678</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6.309220132554671</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.305409628417674</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>62</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2632044956816</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>62</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.4202442623266925</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>62</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-6.711957714496136</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>62</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.505222818285352</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>62</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.536838429266562</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.464894902373986</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>62</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2632044956816</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>62</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7345202387622806</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>62</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.505222818285352</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>62</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.548584904976833</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>62</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.04057542595908007</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25 vs implisit_q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>62</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3992601445192253</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>62</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.04129284669291239</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>62</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.500286399036539</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>62</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.251402137465637</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>62</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.625100704626308</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>62</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4.329833800465674</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>62</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4.225036628407216</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>62</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2.921035993497954</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -764,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,169 +1474,197 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lamandau</t>
+          <t>Kabupaten Sukamara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.543557604810496</v>
+        <v>0.0916716038001323</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Lamandau</t>
+          <t>Kabupaten Sukamara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.543557604810496</v>
+        <v>0.1147817126812041</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Lamandau</t>
+          <t>Kabupaten Sukamara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8557011104512007</v>
+        <v>-7.195416168332211</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Lamandau</t>
+          <t>Kabupaten Sukamara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.135747930615095</v>
+        <v>-10.53102553808372</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Lamandau</t>
+          <t>Kabupaten Sukamara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.234689159883503</v>
+        <v>-6.300852231827034</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Lamandau</t>
+          <t>Kabupaten Sukamara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01283900241414676</v>
+        <v>-6.2337309729091</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01255592085876512</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -978,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,197 +1716,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6210</v>
+        <v>6207</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pulang Pisau</t>
+          <t>Kabupaten Lamandau</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-10.51195191939571</v>
+        <v>0.7338809151401383</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6210</v>
+        <v>6207</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pulang Pisau</t>
+          <t>Kabupaten Lamandau</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-10.51195191939571</v>
+        <v>2.814219268385399</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6210</v>
+        <v>6207</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Pulang Pisau</t>
+          <t>Kabupaten Lamandau</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.09529154660520306</v>
+        <v>-2.810242271039678</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6210</v>
+        <v>6207</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Pulang Pisau</t>
+          <t>Kabupaten Lamandau</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5032370078356028</v>
+        <v>5.061399020797794</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6210</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Pulang Pisau</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.05607550862180165</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6210</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Pulang Pisau</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.02819793704105784</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6210</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Pulang Pisau</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.1269742444645054</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,141 +1874,197 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kapuas</t>
+          <t>Kabupaten Pulang Pisau</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1726138083047084</v>
+        <v>0.5729594432223885</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kapuas</t>
+          <t>Kabupaten Pulang Pisau</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9.44293730718576</v>
+        <v>2.410943689464297</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Kapuas</t>
+          <t>Kabupaten Pulang Pisau</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01107016114757522</v>
+        <v>-8.643498291337412</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Kapuas</t>
+          <t>Kabupaten Pulang Pisau</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.546566675811539</v>
+        <v>-9.209130700947917</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Kapuas</t>
+          <t>Kabupaten Pulang Pisau</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9951281951100877</v>
+        <v>-7.981362283122803</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.5988625151001948</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.156665682884454</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1406,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,57 +2116,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6205</v>
+        <v>6271</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Utara</t>
+          <t>Kota Palangka Raya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1211547523619239</v>
+        <v>0.1291327465986362</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6205</v>
+        <v>6271</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Utara</t>
+          <t>Kota Palangka Raya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.001984324151406429</v>
+        <v>0.1091233872157884</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.86086739248799</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.583345725925772</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01580928835109728</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.20031345270881</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.235091643084513</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.856748750163352</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.175047173003894</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1508,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1545,85 +2414,467 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6208</v>
+        <v>6202</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Seruyan</t>
+          <t>Kabupaten Kotawaringin Timur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4610165080863505</v>
+        <v>-0.1506918380610711</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6208</v>
+        <v>6202</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Seruyan</t>
+          <t>Kabupaten Kotawaringin Timur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.08704642194166953</v>
+        <v>9.92683600095571</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6208</v>
+        <v>6202</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Seruyan</t>
+          <t>Kabupaten Kotawaringin Timur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3231383574725701</v>
+        <v>-3.969094589779029</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-15.53817953167861</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.542934613964941</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.521913225171609</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-7.417472596062466</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.9903951195485192</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.073830829570864</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.547004519806681</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1244202882478474</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-15.21126703095666</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.238151336116473</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.483823565231967</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06397622031350245</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1638,7 +2889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1675,11 +2926,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1688,324 +2939,296 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.528589204053399</v>
+        <v>2.327592470094085</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25_ril vs q-to-q_pkrt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.699146110179489</v>
+        <v>-1.893991044858564</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pkrt_q1-25_ril vs y-on-y_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5996082155996025</v>
+        <v>0.6822449176773556</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.906658131056519</v>
+        <v>1.393475069702663</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.699146110179489</v>
+        <v>24.38330604284439</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pkrt_q1-25_ril vs c-to-c_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.5996082155996025</v>
+        <v>7.841293410557383</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.906658131056519</v>
+        <v>-0.1507920003908291</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.849738605394851</v>
+        <v>2.708563853049023</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9105875220238755</v>
+        <v>0.08551583816291519</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_q_pkrt_q1-25_ril vs sog_q_pkrt_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.900204085656443</v>
+        <v>-1.733656003149575</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkrt_q1-25_ril vs sog_y-on-y_pkrt_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6271</v>
+        <v>6205</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kota Palangka Raya</t>
+          <t>Kabupaten Barito Utara</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01719073710591918</v>
+        <v>-2.083359760503845</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6271</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kota Palangka Raya</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.7140371181926364</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2020,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2057,11 +3280,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2070,54 +3293,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-9.456089918330759</v>
+        <v>5.901788009954769</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-3.937094059989564</v>
+        <v>-5.759128166650954</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2126,324 +3349,268 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1421698465387426</v>
+        <v>3.381084765948267</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-3.937094059989564</v>
+        <v>-2.485246791276182</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1421698465387426</v>
+        <v>5.468228547840232</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04263623307767111</v>
+        <v>9.439298437226528</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.345444484493924</v>
+        <v>-1.360486353154027</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1102696306887196</v>
+        <v>-0.4834917260246938</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.03480369069296696</v>
+        <v>3.440115224896578</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9235952706584455</v>
+        <v>-5.294919091860005</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2105346062282377</v>
+        <v>-1.829763341371025</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Barat</t>
+          <t>Kabupaten Gunung Mas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1003043118797536</v>
+        <v>-1.600750050476603</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>6201</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kabupaten Kotawaringin Barat</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.04130590900257276</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>6201</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kabupaten Kotawaringin Barat</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.05609646739970447</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2458,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2495,11 +3662,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6202</v>
+        <v>6212</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Timur</t>
+          <t>Kabupaten Barito Timur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2508,128 +3675,268 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-4.751021763826436</v>
+        <v>2.063362423241436</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6202</v>
+        <v>6212</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Timur</t>
+          <t>Kabupaten Barito Timur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1897970609667929</v>
+        <v>0.3868077885471963</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6202</v>
+        <v>6212</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Timur</t>
+          <t>Kabupaten Barito Timur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01085397450122437</v>
+        <v>13.71269883951298</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6202</v>
+        <v>6212</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Timur</t>
+          <t>Kabupaten Barito Timur</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.081964501907231</v>
+        <v>7.445722597528547</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6202</v>
+        <v>6212</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Kotawaringin Timur</t>
+          <t>Kabupaten Barito Timur</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04574750593744942</v>
+        <v>7.061216577468858</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.553907207003207</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.30360182651669</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3876682752899866</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2089674258324335</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.387961871907281</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2644,7 +3951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2681,11 +3988,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6204</v>
+        <v>6213</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Selatan</t>
+          <t>Kabupaten Murung Raya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2694,100 +4001,380 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.09633302173040449</v>
+        <v>2.749523179257239</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6204</v>
+        <v>6213</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Selatan</t>
+          <t>Kabupaten Murung Raya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.35785263553277</v>
+        <v>-2.109729004459282</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6204</v>
+        <v>6213</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Selatan</t>
+          <t>Kabupaten Murung Raya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05674900797824185</v>
+        <v>2.848226766526589</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6204</v>
+        <v>6213</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Selatan</t>
+          <t>Kabupaten Murung Raya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.003706872684893865</v>
+        <v>0.7090725594270746</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.62679728997526</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-12.18288422307032</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.800697733741147</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.834233796146033</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.037143207703259</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.6541632374487785</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1630993982512221</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4905745093368346</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.7418512003734162</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.545691514548559</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2802,7 +4389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2839,281 +4426,421 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-9.442043872450135</v>
+        <v>-3.407227487420695</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-6.356707048648468</v>
+        <v>0.01902467312594602</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_q_net_ekspor_q2-25_ril vs sog_q_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.45307703606643</v>
+        <v>-3.220739536444457</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-6.356707048648468</v>
+        <v>0.3744205262825555</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.45307703606643</v>
+        <v>13.12731529521955</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.179593087798413</v>
+        <v>-3.273066838212817</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.062230800050634</v>
+        <v>-20.14121582236178</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1252502442193127</v>
+        <v>2.363664090347091</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09363390754661964</v>
+        <v>-8.811455349498001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6209</v>
+        <v>6203</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kabupaten Katingan</t>
+          <t>Kabupaten Kapuas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.4324973970673469</v>
+        <v>-0.2881281926944263</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.6947465188493646</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.06353861570469369</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.508157565375769</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8.915660165370474</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.880982669749146</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -3128,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3165,225 +4892,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6211</v>
+        <v>6201</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Gunung Mas</t>
+          <t>Kabupaten Kotawaringin Barat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-7.547733622284005</v>
+        <v>-0.190183892508026</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6211</v>
+        <v>6201</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Gunung Mas</t>
+          <t>Kabupaten Kotawaringin Barat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-4.81331138611429</v>
+        <v>-0.2183054008050087</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6211</v>
+        <v>6201</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Gunung Mas</t>
+          <t>Kabupaten Kotawaringin Barat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-4.81331138611429</v>
+        <v>-2.667449138687566</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6211</v>
+        <v>6201</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Gunung Mas</t>
+          <t>Kabupaten Kotawaringin Barat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.017432423535907</v>
+        <v>-14.00134149127121</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6211</v>
+        <v>6201</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Gunung Mas</t>
+          <t>Kabupaten Kotawaringin Barat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05017032710017459</v>
+        <v>-0.4673465437489727</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6211</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Gunung Mas</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1.125312911184333</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6211</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Gunung Mas</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.1535624326372788</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6211</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Gunung Mas</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.1087662197074769</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3398,7 +5041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3435,169 +5078,393 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6212</v>
+        <v>6208</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Timur</t>
+          <t>Kabupaten Seruyan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-6.722159665578506</v>
+        <v>-1.672427116323795</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6212</v>
+        <v>6208</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Timur</t>
+          <t>Kabupaten Seruyan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-6.375842996386042</v>
+        <v>-5.621029528323214</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6212</v>
+        <v>6208</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Timur</t>
+          <t>Kabupaten Seruyan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-6.375842996386042</v>
+        <v>-4.033692799494486</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6212</v>
+        <v>6208</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Timur</t>
+          <t>Kabupaten Seruyan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3533831764558862</v>
+        <v>-1.633544077498752</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6212</v>
+        <v>6208</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Timur</t>
+          <t>Kabupaten Seruyan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05369566008470708</v>
+        <v>-0.0198129457970806</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6212</v>
+        <v>6208</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Timur</t>
+          <t>Kabupaten Seruyan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05813304744802548</v>
+        <v>-16.66439671593581</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-5.029274439349128</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04602171162795549</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-7.077345395166783</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-10.22764154198773</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-5.397775880516114</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-4.310773563265063</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.42318138783694</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.30654548958874</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3612,7 +5479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3649,113 +5516,225 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6213</v>
+        <v>6204</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Murung Raya</t>
+          <t>Kabupaten Barito Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03704165248623766</v>
+        <v>3.227344892104526</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6213</v>
+        <v>6204</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Murung Raya</t>
+          <t>Kabupaten Barito Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7071150187984232</v>
+        <v>16.08303161113955</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6213</v>
+        <v>6204</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Murung Raya</t>
+          <t>Kabupaten Barito Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5450780829086873</v>
+        <v>7.226343798675494</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6213</v>
+        <v>6204</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Murung Raya</t>
+          <t>Kabupaten Barito Selatan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0002086955313965507</v>
+        <v>2.825000695368772</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.121207137532737</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.439953230434016</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2024261628816648</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1168437905698965</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_62.xlsx
+++ b/data/output/evaluasi_62.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
